--- a/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/bio-bio.xlsx
+++ b/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/bio-bio.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>5791.89</v>
+        <v>5667.28</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>35483.34</v>
+        <v>34533.22</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>27119.25</v>
+        <v>26393.09</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>65683.16</v>
+        <v>63924.39</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>41430.64</v>
+        <v>40321.27</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>3508.24</v>
+        <v>3519.28</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>25615.72</v>
+        <v>25721.89</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>13179.03</v>
+        <v>13145.76</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>38501.05</v>
+        <v>38082.22</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>38501.05</v>
+        <v>38082.22</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>103347.8</v>
+        <v>104061.33</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>10624.49</v>
+        <v>10697.85</v>
       </c>
     </row>
     <row r="14">
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>17934.88</v>
+        <v>17887.44</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2416-170-CM26</t>
+          <t>2416-171-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>2213.9</v>
+        <v>1345.75</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2416-171-CM26</t>
+          <t>2416-170-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>1372.62</v>
+        <v>2170.56</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>40049.63</v>
+        <v>40430.05</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>12825.33</v>
+        <v>12890.69</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>5370.74</v>
+        <v>5391.65</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>12352.71</v>
+        <v>12400.79</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>16112.23</v>
+        <v>16061.33</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>46725.46</v>
+        <v>46631.79</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>44061.57</v>
+        <v>43355.11</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>9183.969999999999</v>
+        <v>9133.049999999999</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>43412.78</v>
+        <v>43703.37</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,129 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>16477.44</v>
+        <v>16587.73</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2408-724-CM26</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>69.170.100-K</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Bío-Bío</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>TURISMO AYEKANTUN LIMITADA</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>76.470.279-4</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="n">
+        <v>14179.41</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2408-777-CM26</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>69.170.100-K</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Bío-Bío</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>TURISMO AYEKANTUN LIMITADA</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>76.470.279-4</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="n">
+        <v>10663.29</v>
       </c>
     </row>
   </sheetData>
